--- a/duoki_editor/resources/data/blank/餐厅-一般疑问句_否定答句认读-1-blank.xlsx
+++ b/duoki_editor/resources/data/blank/餐厅-一般疑问句_否定答句认读-1-blank.xlsx
@@ -61,7 +61,7 @@
     <t>一般疑问句_认读_1_问_2</t>
   </si>
   <si>
-    <t>一般疑问句_认读_1_问_答案</t>
+    <t>(一般疑问句_认读_1_问_答案)</t>
   </si>
   <si>
     <t>一般疑问句_认读_1_帮助</t>
@@ -103,13 +103,13 @@
     <t>我来帮你吧！ {sentence_answer_en_2}</t>
   </si>
   <si>
-    <t>Wow！挑战成功！你们赢得了我所有的宝石，一共20颗！我得再去取一些宝石啦，下次再来找你们！See you！</t>
-  </si>
-  <si>
-    <t>这次{npc2_name}帮了你，只能得到10颗宝石哦！我还会再来找你们，下要继续加油！</t>
-  </si>
-  <si>
-    <t>20|10</t>
+    <t>Wow！挑战成功！你们赢得了我所有的宝石，一共10颗！我得再去取一些宝石啦，下次再来找你们！See you！</t>
+  </si>
+  <si>
+    <t>这次{npc2_name}帮了你，只能得到5颗宝石哦！我还会再来找你们，下要继续加油！</t>
+  </si>
+  <si>
+    <t>10|5</t>
   </si>
 </sst>
 </file>
